--- a/AAII_Financials/Quarterly/TFC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TFC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
   <si>
     <t>TFC</t>
   </si>
@@ -656,241 +656,247 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4870000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4673000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4734000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4751000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4499000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4441000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4589000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4637000</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M8" s="3">
         <v>4318000</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O8" s="3">
         <v>4372000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4445000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4786000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5238000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4369000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3673000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3357000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3411000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3426000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3443000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3494000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3611000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3623000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3888000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4426000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2812000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2218000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2206000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2173000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2136000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2069000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1994000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1921000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1898000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -996,53 +1002,56 @@
       <c r="AK9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4870000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4673000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4734000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4751000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4499000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4441000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4589000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4637000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-2136000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4318000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O10" s="3">
         <v>4372000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4445000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4786000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1103,8 +1112,11 @@
       <c r="AK10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1142,8 +1154,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1249,8 +1262,11 @@
       <c r="AK12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1356,53 +1372,56 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>-93000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>27000</v>
       </c>
-      <c r="G14" s="3">
-        <v>28000</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>-109000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>25000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>46000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>126000</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="3">
         <v>61000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>48000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>56000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1463,115 +1482,121 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>191000</v>
+      </c>
+      <c r="E15" s="3">
         <v>193000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>302000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>171000</v>
       </c>
-      <c r="G15" s="3">
-        <v>179000</v>
-      </c>
       <c r="H15" s="3">
+        <v>212000</v>
+      </c>
+      <c r="I15" s="3">
         <v>220000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>345000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>195000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>206000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>212000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>122000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>259000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>257000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>270000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-163000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-140000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-143000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-137000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-143000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-145000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-142000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-144000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-172000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-170000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-178000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-165000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-71000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-29000</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>-32000</v>
       </c>
       <c r="AF15" s="3">
         <v>-32000</v>
       </c>
       <c r="AG15" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="AH15" s="3">
         <v>-34000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-33000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-31000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-33000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-34000</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1606,222 +1631,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2931000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2851000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3186000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2883000</v>
       </c>
-      <c r="G17" s="3">
-        <v>2830000</v>
-      </c>
       <c r="H17" s="3">
+        <v>2858000</v>
+      </c>
+      <c r="I17" s="3">
         <v>2762000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3004000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2767000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2887000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2662000</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O17" s="3">
         <v>2824000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2826000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2784000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1724000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>858000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>437000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>79000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>65000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>-131000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>-236000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>257000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>245000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>261000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>440000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>776000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>756000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>635000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>688000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>632000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>577000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>517000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>472000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>438000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>392000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1939000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1822000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1548000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1868000</v>
       </c>
-      <c r="G18" s="3">
-        <v>1669000</v>
-      </c>
       <c r="H18" s="3">
+        <v>1641000</v>
+      </c>
+      <c r="I18" s="3">
         <v>1679000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1585000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1870000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5023000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1656000</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O18" s="3">
         <v>1548000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1619000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2002000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3514000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3511000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3236000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3278000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3346000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3557000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3679000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3237000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3366000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3362000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3448000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3650000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2056000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1583000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1518000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1541000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1559000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1552000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1522000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1483000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1506000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1859,222 +1891,229 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E20" s="3">
         <v>132000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>77000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>104000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>128000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>144000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>140000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>135000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>161000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>165000</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O20" s="3">
         <v>175000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>172000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>175000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1495000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1511000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1332000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1532000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1377000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1430000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1606000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1413000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1725000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1966000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2299000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2363000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1177000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-537000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-399000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-566000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-549000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-503000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-498000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-506000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-630000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2006000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1883000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1773000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1935000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1720000</v>
-      </c>
       <c r="H21" s="3">
+        <v>1725000</v>
+      </c>
+      <c r="I21" s="3">
         <v>1755000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1790000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1930000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4978000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1703000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>122000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1632000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1704000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2097000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2384000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2324000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2249000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2078000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2312000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2481000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2415000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2169000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2042000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1784000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1569000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1686000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1092000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1187000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1258000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1112000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1152000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1188000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1160000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1115000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1013000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2117,8 +2156,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2180,222 +2219,231 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1815000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1690000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1564000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1737000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1513000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1535000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1554000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1710000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5230000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1365000</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O23" s="3">
         <v>1312000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1399000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1771000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2019000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2000000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1904000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1746000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1969000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2127000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2073000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1824000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1641000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1396000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1149000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1287000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>879000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1046000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1119000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>975000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1010000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1049000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1024000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>977000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>876000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>262000</v>
+      </c>
+      <c r="E24" s="3">
         <v>209000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>210000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>285000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>273000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>274000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>265000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>271000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1324000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>232000</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O24" s="3">
         <v>203000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>230000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>361000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>337000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>363000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>372000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>330000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>367000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>423000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>415000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>351000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>311000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>255000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>191000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>224000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>153000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>218000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>234000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>177000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>232000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>210000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>202000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>186000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>252000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2501,222 +2549,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1553000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1481000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1354000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1452000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1240000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1261000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1289000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1439000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3906000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1133000</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O26" s="3">
         <v>1109000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1169000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1410000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1682000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1637000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1532000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1416000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1602000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1704000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1658000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1473000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1330000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1141000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>958000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1063000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>726000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>828000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>885000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>798000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>778000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>839000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>822000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>791000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>624000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1519000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1377000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1289000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1348000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1180000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1157000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1216000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1336000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>826000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1091000</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O27" s="3">
         <v>1071000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1234000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1410000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1610000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1536000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1454000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1327000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1524000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1616000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1559000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1334000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1228000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1068000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>902000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>986000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>702000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>735000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>842000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>749000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>727000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>789000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>775000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>745000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>571000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2822,8 +2879,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2843,37 +2903,37 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-13000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>3000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>4809000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>64000</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>68000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>140000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>103000</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="S29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
@@ -2896,17 +2956,17 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
@@ -2914,23 +2974,26 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3">
         <v>27000</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>43000</v>
       </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3036,8 +3099,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3143,222 +3209,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-124000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-132000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-77000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-104000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-128000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-144000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-140000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-135000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-161000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-165000</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O32" s="3">
         <v>-175000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-172000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-175000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1495000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1511000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1332000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1532000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1377000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1430000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1606000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1413000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1725000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1966000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2299000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2363000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1177000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>537000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>399000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>566000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>549000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>503000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>498000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>506000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>630000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1553000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1481000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1354000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1452000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1240000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1261000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1276000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1442000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>903000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1197000</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O33" s="3">
         <v>1177000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1309000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1513000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1610000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1536000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1454000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1327000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1524000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1616000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1559000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1334000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1228000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1068000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>902000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>986000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>702000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>735000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>842000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>749000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>754000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>789000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>775000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>745000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>614000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3464,227 +3539,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1553000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1481000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1354000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1452000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1240000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1261000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1276000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1442000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>903000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1197000</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O35" s="3">
         <v>1177000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1309000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1513000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1610000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1536000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1454000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1327000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1524000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1616000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1559000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1334000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1228000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1068000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>902000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>986000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>702000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>735000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>842000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>749000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>754000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>789000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>775000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>745000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>614000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3722,8 +3806,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3761,267 +3846,274 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>39288000</v>
+      </c>
+      <c r="E41" s="3">
         <v>36197000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>36377000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>36852000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>41451000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>42171000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>39768000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>39640000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>40879000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>34550000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>30230000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>29832000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>30010000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>37596000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5379000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5031000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5511000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5516000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5085000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4656000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5077000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5097000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5029000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4194000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5116000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5312000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4084000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2027000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1831000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1873000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2753000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2123000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2046000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1869000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2243000</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>11174000</v>
+      </c>
+      <c r="E42" s="3">
         <v>10648000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>10333000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>10396000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>10266000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9704000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>8616000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>9523000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>8991000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>8447000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>7661000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>7151000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>7217000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>8930000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>24812000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>26766000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>26868000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>33961000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>23661000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>27086000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>31946000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>36528000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>23457000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>43098000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>45693000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>42150000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>22131000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>980000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>855000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1004000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1128000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>884000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>876000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1045000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>513000</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1670000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2122000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1624000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2126000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2094000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2241000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1904000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1600000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1046000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1246000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>997000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2659000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3129000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2763000</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4082,53 +4174,56 @@
       <c r="AK43" s="3">
         <v>0</v>
       </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>5</v>
+      <c r="D44" s="3">
+        <v>56000</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3">
         <v>58000</v>
       </c>
-      <c r="G44" s="3">
-        <v>1032000</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3">
         <v>53000</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L44" s="3">
         <v>56000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>60000</v>
-      </c>
-      <c r="M44" s="3">
-        <v>57000</v>
       </c>
       <c r="N44" s="3">
         <v>57000</v>
       </c>
       <c r="O44" s="3">
+        <v>57000</v>
+      </c>
+      <c r="P44" s="3">
         <v>59000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>69000</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
@@ -4189,53 +4284,56 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1963000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1968000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2028000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2093000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2017000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2053000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2069000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2114000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2113000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9806000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9740000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2335000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2133000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2429000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4296,53 +4394,56 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>57807000</v>
+      </c>
+      <c r="E46" s="3">
         <v>54189000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>53320000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>54513000</v>
       </c>
-      <c r="G46" s="3">
-        <v>59161000</v>
-      </c>
       <c r="H46" s="3">
+        <v>58129000</v>
+      </c>
+      <c r="I46" s="3">
         <v>58441000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>54806000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>55181000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>55579000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>56505000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>51048000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>44590000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>45675000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>55124000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4403,53 +4504,56 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>126148000</v>
+      </c>
+      <c r="E47" s="3">
         <v>123532000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>123631000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>124644000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>126093000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>128305000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>128372000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>125051000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>117912000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>128707000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>130569000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>129122000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>134034000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>138803000</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -4510,222 +4614,231 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5216000</v>
+      </c>
+      <c r="E48" s="3">
         <v>5464000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5576000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5661000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5690000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5634000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5592000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5643000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5745000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6062000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6002000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6420000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6626000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6729000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4798000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4701000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4777000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4788000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3700000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4926000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4932000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5064000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5203000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5515000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5726000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5772000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5535000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2863000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2871000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2900000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2118000</v>
-      </c>
-      <c r="AH48" s="3">
-        <v>2154000</v>
       </c>
       <c r="AI48" s="3">
         <v>2154000</v>
       </c>
       <c r="AJ48" s="3">
+        <v>2154000</v>
+      </c>
+      <c r="AK48" s="3">
         <v>2078000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2055000</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>22548000</v>
+      </c>
+      <c r="E49" s="3">
         <v>22429000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>22353000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>22229000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>22136000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>22226000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>22383000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>22259000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>22296000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>22390000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>22443000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>33808000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>33913000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>33852000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>34443000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>34333000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>33300000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>32990000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>32139000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>30405000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>29270000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>29546000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>29454000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>28700000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>28975000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>29245000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>29926000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>11429000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>11512000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>11580000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>11684000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>11800000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>11407000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>11415000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>11385000</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4831,8 +4944,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4938,89 +5054,92 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>17704000</v>
+      </c>
+      <c r="E52" s="3">
         <v>17730000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>17586000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>16410000</v>
       </c>
-      <c r="G52" s="3">
-        <v>15229000</v>
-      </c>
       <c r="H52" s="3">
+        <v>16261000</v>
+      </c>
+      <c r="I52" s="3">
         <v>15951000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>16552000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15665000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15498000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15616000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14987000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14216000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>14133000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>14259000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4539000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6464000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6406000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6348000</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V52" s="3">
+      <c r="V52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W52" s="3">
         <v>4814000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4837000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4810000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4358000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3996000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3946000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3915000</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>5</v>
       </c>
@@ -5036,8 +5155,8 @@
       <c r="AH52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI52" s="3">
-        <v>0</v>
+      <c r="AI52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AJ52" s="3">
         <v>0</v>
@@ -5045,8 +5164,11 @@
       <c r="AK52" s="3">
         <v>0</v>
       </c>
+      <c r="AL52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5152,115 +5274,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>556023000</v>
+      </c>
+      <c r="E54" s="3">
         <v>548975000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>547538000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>543851000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>543833000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>535899000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>531176000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>523434000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>519853000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>534959000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>535349000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>542707000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>554549000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>574354000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>555255000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>548438000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>545123000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>543979000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>541241000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>529884000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>521964000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>517537000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>509228000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>499183000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>504336000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>506229000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>473078000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>236750000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>230872000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>227683000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>225697000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>222885000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>222681000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>220729000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>221642000</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5298,8 +5426,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5337,160 +5466,164 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>409379000</v>
+      </c>
+      <c r="E57" s="3">
         <v>404081000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>400398000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>394907000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>406122000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>403736000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>390524000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>387778000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>385411000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>394265000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>395865000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>400024000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>406043000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>404997000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>13053000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>13299000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>11839000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10158000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>12677000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>10370000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>9986000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>8645000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>9654000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>9284000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>9324000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>9552000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>10115000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>5274000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>5642000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>5041000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>5433000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>5434000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>5717000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>5140000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>5990000</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>34126000</v>
+      </c>
+      <c r="E58" s="3">
         <v>34976000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>34382000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>34994000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>20191000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>25994000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>33235000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>22771000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>25555000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>29319000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>31595000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>26959000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>27584000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>26267000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -5551,8 +5684,11 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5580,77 +5716,77 @@
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M59" s="3">
         <v>3122000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3539000</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R59" s="3">
         <v>1545000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1477000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1471000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1529000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1600000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1694000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1742000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1812000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1896000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1927000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2061000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2079000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2121000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>968000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>961000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>959000</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI59" s="3">
-        <v>0</v>
+      <c r="AI59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AJ59" s="3">
         <v>0</v>
@@ -5658,53 +5794,56 @@
       <c r="AK59" s="3">
         <v>0</v>
       </c>
+      <c r="AL59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>443505000</v>
+      </c>
+      <c r="E60" s="3">
         <v>439057000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>434780000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>429901000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>426313000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>429730000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>423759000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>410549000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>410966000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>426706000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>430999000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>426983000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>433627000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>431264000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -5765,165 +5904,171 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>39169000</v>
+      </c>
+      <c r="E61" s="3">
         <v>37230000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>38493000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>39211000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>43982000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>32792000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>34513000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>37990000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>35899000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>40426000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>36135000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>42668000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>46209000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>71393000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>43201000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>31170000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>30316000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>32913000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>35050000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>36970000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>36821000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>36879000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>38583000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>40127000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>39499000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>65662000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>37198000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>23880000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>20897000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>22983000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>21960000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>20799000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>21641000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>20959000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>21168000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9254000</v>
+      </c>
+      <c r="E62" s="3">
         <v>8474000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8447000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9093000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8698000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8742000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8660000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9199000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9161000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8774000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8303000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>11049000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>11032000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9303000</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
+      <c r="S62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T62" s="3">
         <v>0</v>
@@ -5979,8 +6124,11 @@
       <c r="AK62" s="3">
         <v>0</v>
       </c>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6086,8 +6234,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6193,8 +6344,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6300,115 +6454,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>491928000</v>
+      </c>
+      <c r="E66" s="3">
         <v>484761000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>482349000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>478205000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>478993000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>471264000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>467497000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>457738000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>456026000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>475906000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>476096000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>480700000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>490868000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>511960000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>494741000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>487650000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>482148000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>478958000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>471970000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>460984000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>453628000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>449661000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>438421000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>429316000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>435559000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>440335000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>406694000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>204516000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>199169000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>196860000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>195575000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>192937000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>192901000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>191117000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>191994000</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6446,8 +6606,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6553,8 +6714,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6660,19 +6824,22 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>4916000</v>
+        <v>5411000</v>
       </c>
       <c r="E70" s="3">
         <v>4916000</v>
       </c>
       <c r="F70" s="3">
-        <v>5907000</v>
+        <v>4916000</v>
       </c>
       <c r="G70" s="3">
         <v>5907000</v>
@@ -6684,7 +6851,7 @@
         <v>5907000</v>
       </c>
       <c r="J70" s="3">
-        <v>6673000</v>
+        <v>5907000</v>
       </c>
       <c r="K70" s="3">
         <v>6673000</v>
@@ -6726,28 +6893,28 @@
         <v>6673000</v>
       </c>
       <c r="X70" s="3">
+        <v>6673000</v>
+      </c>
+      <c r="Y70" s="3">
         <v>7124000</v>
-      </c>
-      <c r="Y70" s="3">
-        <v>8048000</v>
       </c>
       <c r="Z70" s="3">
         <v>8048000</v>
       </c>
       <c r="AA70" s="3">
+        <v>8048000</v>
+      </c>
+      <c r="AB70" s="3">
         <v>7143000</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>4599000</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>5102000</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>3057000</v>
-      </c>
-      <c r="AE70" s="3">
-        <v>3053000</v>
       </c>
       <c r="AF70" s="3">
         <v>3053000</v>
@@ -6767,8 +6934,11 @@
       <c r="AK70" s="3">
         <v>3053000</v>
       </c>
+      <c r="AL70" s="3">
+        <v>3053000</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6874,115 +7044,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>27676000</v>
+      </c>
+      <c r="E72" s="3">
         <v>26796000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>26067000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>25438000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>24759000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>24252000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>23777000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>23248000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>22603000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>22483000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>22088000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>27944000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>27577000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>27038000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>26264000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>25344000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>24500000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>23687000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>22998000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>22114000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>21139000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>20184000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>19455000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>18834000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>18373000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>18076000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>19806000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>19440000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>19050000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>18518000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>18118000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>17673000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>17197000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>16712000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>16259000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7088,8 +7264,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7195,8 +7374,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7302,115 +7484,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>58684000</v>
+      </c>
+      <c r="E76" s="3">
         <v>59298000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>60273000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>59739000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>58933000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>58728000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>57772000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>59023000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>57154000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>52148000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>52428000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>55167000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>56853000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>55699000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>53841000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>54115000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>56302000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>58348000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>62598000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>62227000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>61663000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>60752000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>62759000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>61819000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>61634000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>61295000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>61282000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>29177000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>28650000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>27770000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>27069000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>26895000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>26727000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>26559000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>26595000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7516,227 +7704,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1553000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1481000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1354000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1452000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1240000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1261000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1276000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1442000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>903000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1197000</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O81" s="3">
         <v>1177000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1309000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1513000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1610000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1536000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1454000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1327000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1524000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1616000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1559000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1334000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1228000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1068000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>902000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>986000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>702000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>735000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>842000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>749000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>754000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>789000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>775000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>745000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>614000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7774,115 +7971,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>139000</v>
+      </c>
+      <c r="E83" s="3">
         <v>145000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>153000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>145000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>151000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>164000</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K83" s="3">
         <v>172000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>170000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>180000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>202000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>184000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>202000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>195000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>365000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>324000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>345000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>332000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>343000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>354000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>342000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>345000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>401000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>388000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>420000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>399000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>213000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>141000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>139000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>137000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>142000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>139000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>136000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>138000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>137000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7988,8 +8189,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8095,8 +8299,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8202,8 +8409,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8309,8 +8519,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8416,115 +8629,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1039000</v>
+      </c>
+      <c r="E89" s="3">
         <v>679000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2582000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1497000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>914000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>746000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>775000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1534000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>845000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-990000</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O89" s="3">
         <v>2407000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3730000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>118000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3534000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3770000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3965000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-188000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4807000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-218000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3336000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-33000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2408000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>425000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-24000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>4628000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-444000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1775000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>934000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-745000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1371000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1551000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1119000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>308000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1676000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8562,8 +8781,9 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8597,23 +8817,23 @@
       <c r="M91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N91" s="3">
+      <c r="N91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O91" s="3">
         <v>-15000</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
       <c r="S91" s="3">
-        <v>-130000</v>
+        <v>0</v>
       </c>
       <c r="T91" s="3">
         <v>-130000</v>
@@ -8625,43 +8845,43 @@
         <v>-130000</v>
       </c>
       <c r="W91" s="3">
+        <v>-130000</v>
+      </c>
+      <c r="X91" s="3">
         <v>-76000</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-99000</v>
       </c>
       <c r="Y91" s="3">
         <v>-99000</v>
       </c>
       <c r="Z91" s="3">
+        <v>-99000</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-130000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-122000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-464000</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD91" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AE91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AF91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-34000</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI91" s="3">
-        <v>0</v>
+      <c r="AI91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AJ91" s="3">
         <v>0</v>
@@ -8669,8 +8889,11 @@
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8776,8 +8999,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8883,115 +9109,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2872000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1937000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4792000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3635000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7705000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1631000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7960000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3494000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>24149000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>5903000</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O94" s="3">
         <v>8348000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>11567000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2050000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10763000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-8404000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-10771000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-34000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-12134000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-12897000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-10144000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>3119000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-29565000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2118000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>7546000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-19515000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>17719000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-6564000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2330000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-477000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2214000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1170000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1766000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>203000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-2166000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9029,115 +9261,119 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>636000</v>
+      </c>
+      <c r="E96" s="3">
         <v>645000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>658000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>665000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>670000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>679000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>685000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>695000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>696000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>694000</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N96" s="3">
-        <v>693000</v>
+      <c r="N96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O96" s="3">
         <v>693000</v>
       </c>
       <c r="P96" s="3">
+        <v>693000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>691000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-689000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-691000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-639000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-637000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-638000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-640000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-602000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-605000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-607000</v>
       </c>
       <c r="Z96" s="3">
         <v>-607000</v>
       </c>
       <c r="AA96" s="3">
-        <v>-605000</v>
+        <v>-607000</v>
       </c>
       <c r="AB96" s="3">
         <v>-605000</v>
       </c>
       <c r="AC96" s="3">
-        <v>-345000</v>
+        <v>-605000</v>
       </c>
       <c r="AD96" s="3">
         <v>-345000</v>
       </c>
       <c r="AE96" s="3">
+        <v>-345000</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-310000</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-309000</v>
       </c>
       <c r="AG96" s="3">
         <v>-309000</v>
       </c>
       <c r="AH96" s="3">
+        <v>-309000</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-313000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-290000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-292000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-258000</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9243,8 +9479,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9350,8 +9589,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9457,115 +9699,121 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4924000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1078000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1735000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2461000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6071000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3288000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>7313000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>721000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-19100000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-572000</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O100" s="3">
         <v>-10933000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-21883000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>17107000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>6425000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3746000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>797000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>9049000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>7795000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>6385000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1233000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>10178000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>8917000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2396000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2673000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>32170000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1114000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>5135000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1125000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>207000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1677000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-281000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>589000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-483000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>505000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9608,8 +9856,8 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -9671,111 +9919,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3091000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-180000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-475000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4599000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-720000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2403000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>128000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1239000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5894000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4341000</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>-178000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6586000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>15175000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-804000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-888000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6009000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>8827000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>468000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-6730000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-5575000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>13264000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-18240000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-4089000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>4849000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>17283000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>16161000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>346000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-271000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1015000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>834000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>100000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-58000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>28000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>15000</v>
       </c>
     </row>
